--- a/BadGolf_Admin_Queue_2026-08-28.xlsx
+++ b/BadGolf_Admin_Queue_2026-08-28.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Bad Golf — open admin queue</t>
   </si>
   <si>
-    <t xml:space="preserve">29 open items — this is the whole queue, read from the live database on 28 Aug 2026 and sorted by what needs doing. 669 dead tickets belonging to 529 courses that had already been deleted from the library were removed from the database on the same date, so the queue and this sheet now match exactly.</t>
+    <t xml:space="preserve">29 open items — this is the whole queue, read from the live database on 28 Aug 2026 and sorted by what needs doing. 669 dead tickets belonging to 529 courses that had already been deleted from the library were removed from the database on the same date, so the queue and this sheet now match exactly. The "Button in Admin" column is what Kevin will see on build v2026.11.1280: "Close out" on the 15 he has already signed off, "Complete" on the rest. Press it only once the Action column is actually done — on a row that says Map or HOLD, the work comes first.</t>
   </si>
   <si>
     <t xml:space="preserve">State</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Rated tees</t>
   </si>
   <si>
-    <t xml:space="preserve">Kevin signed off?</t>
+    <t xml:space="preserve">Button in Admin</t>
   </si>
   <si>
     <t xml:space="preserve">Raised</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">Scottsdale</t>
   </si>
   <si>
-    <t xml:space="preserve">Looks done — tap Complete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All three nines are fully mapped and the card has 5 rated tees. Nothing outstanding was recorded on the ticket. Open it in Admin and tap the new ✅ Complete button to clear it.</t>
+    <t xml:space="preserve">Looks done — close it out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All three nines are fully mapped and the card has 5 rated tees. Nothing outstanding was recorded on the ticket — it is only still listed because an old code-review item outranks the sign-off. Tap ✅ Close out on the card and it is done. Good one to try the new button on first.</t>
   </si>
   <si>
     <t xml:space="preserve">Arroyo 9/9, Dunes 9/9, Lakes 9/9</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes</t>
+    <t xml:space="preserve">✅ Close out</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-26</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Map the Blue nine only (9 greens + fairway targets). Red and White are done — do not remap them.</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
+    <t xml:space="preserve">✅ Complete</t>
   </si>
   <si>
     <t xml:space="preserve">little-mill-country-club</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">Who does it</t>
   </si>
   <si>
-    <t xml:space="preserve">Kevin — one tap each</t>
+    <t xml:space="preserve">Kevin — one tap</t>
   </si>
   <si>
     <t xml:space="preserve">Map — new nines on a 27-hole club</t>
@@ -1208,7 +1208,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="44"/>
   </cols>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
